--- a/apps/web/public/templates/school-precise-student-template.xlsx
+++ b/apps/web/public/templates/school-precise-student-template.xlsx
@@ -51,39 +51,46 @@
     <comment ref="E1" authorId="0">
       <text>
         <r>
-          <t>Choose Male or Female from the list.</t>
+          <t>The day the student joined the school, day first: 14/09/2026. Optional.</t>
         </r>
       </text>
     </comment>
     <comment ref="F1" authorId="0">
       <text>
         <r>
-          <t>Exactly as the class is named on the Classes page, e.g. JSS 1A. Create your classes before importing. Leave blank to place the student later.</t>
+          <t>Choose Male or Female from the list.</t>
         </r>
       </text>
     </comment>
     <comment ref="G1" authorId="0">
       <text>
         <r>
-          <t>Optional, e.g. A or Gold.</t>
+          <t>Exactly as the class is named on the Classes page, e.g. JSS 1A. Create your classes before importing. Leave blank to place the student later.</t>
         </r>
       </text>
     </comment>
     <comment ref="H1" authorId="0">
       <text>
         <r>
-          <t>Optional. Used to invite the parent to their child's page.</t>
+          <t>Optional, e.g. A or Gold.</t>
         </r>
       </text>
     </comment>
     <comment ref="I1" authorId="0">
       <text>
         <r>
+          <t>Optional. Used to invite the parent to their child's page.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
           <t>Optional, e.g. 08031234567. Kept as text so the first 0 isn't lost.</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <t>Optional. Home address.</t>
@@ -95,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="30">
   <si>
     <t>First Name</t>
   </si>
@@ -107,6 +114,9 @@
   </si>
   <si>
     <t>Date of Birth</t>
+  </si>
+  <si>
+    <t>Admission Date</t>
   </si>
   <si>
     <t>Gender</t>
@@ -148,7 +158,7 @@
     <t>Dark green headings are required: First Name, Last Name and Admission Number. The rest are optional but recommended.</t>
   </si>
   <si>
-    <t>Date of Birth: day first, e.g. 14/03/2015.   Gender: choose Male or Female from the list.   Parent Phone: e.g. 08031234567.</t>
+    <t>Date of Birth and Admission Date: day first, e.g. 14/03/2015.   Gender: choose Male or Female from the list.   Parent Phone: e.g. 08031234567.</t>
   </si>
   <si>
     <t>Keep the headings in row 1 exactly as they are. Don't add notes or blank rows above the students. Up to 500 students per upload.</t>
@@ -178,7 +188,7 @@
     <t>Example (don't type this into the Students sheet)</t>
   </si>
   <si>
-    <t>Chiamaka | Eze | GFA/2026/014 | 14/03/2015 | Female | JSS 1A | A | parent@gmail.com | 08031234567 | 12 Admiralty Way, Lekki</t>
+    <t>Chiamaka | Eze | GFA/2026/014 | 14/03/2015 | 14/09/2026 | Female | JSS 1A | A | parent@gmail.com | 08031234567 | 12 Admiralty Way, Lekki</t>
   </si>
   <si>
     <t>Need help? Email hello@schoolprecise.com or use the chat on schoolprecise.com.</t>
@@ -627,21 +637,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J501"/>
+  <dimension ref="A1:K501"/>
   <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="20" style="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" customWidth="1"/>
-    <col min="10" max="10" width="34" customWidth="1"/>
+    <col min="5" max="5" width="16" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+    <col min="10" max="10" width="16" style="1" customWidth="1"/>
+    <col min="11" max="11" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -654,7 +665,7 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
@@ -666,2519 +677,3022 @@
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E2" s="1"/>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E3" s="1"/>
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E4" s="1"/>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E5" s="1"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E6" s="1"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E7" s="1"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E8" s="1"/>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E9" s="1"/>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E11" s="1"/>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E12" s="1"/>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E13" s="1"/>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E14" s="1"/>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="I15" s="1"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E15" s="1"/>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E16" s="1"/>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E17" s="1"/>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E18" s="1"/>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E19" s="1"/>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E20" s="1"/>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E21" s="1"/>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E22" s="1"/>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
-      <c r="I23" s="1"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E23" s="1"/>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
-      <c r="I24" s="1"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E24" s="1"/>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E25" s="1"/>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E26" s="1"/>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
-      <c r="I27" s="1"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E27" s="1"/>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
-      <c r="I28" s="1"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E28" s="1"/>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
-      <c r="I29" s="1"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E29" s="1"/>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E30" s="1"/>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E31" s="1"/>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E32" s="1"/>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E33" s="1"/>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="I34" s="1"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E34" s="1"/>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E35" s="1"/>
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="I36" s="1"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E36" s="1"/>
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="I37" s="1"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E37" s="1"/>
+      <c r="J37" s="1"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="I38" s="1"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E38" s="1"/>
+      <c r="J38" s="1"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E39" s="1"/>
+      <c r="J39" s="1"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E40" s="1"/>
+      <c r="J40" s="1"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="I41" s="1"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E41" s="1"/>
+      <c r="J41" s="1"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E42" s="1"/>
+      <c r="J42" s="1"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E43" s="1"/>
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="I44" s="1"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E44" s="1"/>
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
-      <c r="I45" s="1"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E45" s="1"/>
+      <c r="J45" s="1"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
-      <c r="I46" s="1"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E46" s="1"/>
+      <c r="J46" s="1"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
-      <c r="I47" s="1"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E47" s="1"/>
+      <c r="J47" s="1"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="I48" s="1"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E48" s="1"/>
+      <c r="J48" s="1"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="I49" s="1"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E49" s="1"/>
+      <c r="J49" s="1"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="I50" s="1"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E50" s="1"/>
+      <c r="J50" s="1"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
-      <c r="I51" s="1"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E51" s="1"/>
+      <c r="J51" s="1"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="I52" s="1"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E52" s="1"/>
+      <c r="J52" s="1"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
-      <c r="I53" s="1"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E53" s="1"/>
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
-      <c r="I54" s="1"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E54" s="1"/>
+      <c r="J54" s="1"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
-      <c r="I55" s="1"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E55" s="1"/>
+      <c r="J55" s="1"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
-      <c r="I56" s="1"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E56" s="1"/>
+      <c r="J56" s="1"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
-      <c r="I57" s="1"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E57" s="1"/>
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
-      <c r="I58" s="1"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E58" s="1"/>
+      <c r="J58" s="1"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
-      <c r="I59" s="1"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E59" s="1"/>
+      <c r="J59" s="1"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
-      <c r="I60" s="1"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E60" s="1"/>
+      <c r="J60" s="1"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
-      <c r="I61" s="1"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E61" s="1"/>
+      <c r="J61" s="1"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
-      <c r="I62" s="1"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E62" s="1"/>
+      <c r="J62" s="1"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
-      <c r="I63" s="1"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E63" s="1"/>
+      <c r="J63" s="1"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
-      <c r="I64" s="1"/>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E64" s="1"/>
+      <c r="J64" s="1"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
-      <c r="I65" s="1"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E65" s="1"/>
+      <c r="J65" s="1"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
-      <c r="I66" s="1"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E66" s="1"/>
+      <c r="J66" s="1"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
-      <c r="I67" s="1"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E67" s="1"/>
+      <c r="J67" s="1"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
-      <c r="I68" s="1"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E68" s="1"/>
+      <c r="J68" s="1"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
-      <c r="I69" s="1"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E69" s="1"/>
+      <c r="J69" s="1"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
-      <c r="I70" s="1"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E70" s="1"/>
+      <c r="J70" s="1"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
-      <c r="I71" s="1"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E71" s="1"/>
+      <c r="J71" s="1"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
-      <c r="I72" s="1"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E72" s="1"/>
+      <c r="J72" s="1"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
-      <c r="I73" s="1"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E73" s="1"/>
+      <c r="J73" s="1"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
-      <c r="I74" s="1"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E74" s="1"/>
+      <c r="J74" s="1"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
-      <c r="I75" s="1"/>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E75" s="1"/>
+      <c r="J75" s="1"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
-      <c r="I76" s="1"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E76" s="1"/>
+      <c r="J76" s="1"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
-      <c r="I77" s="1"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E77" s="1"/>
+      <c r="J77" s="1"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
-      <c r="I78" s="1"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E78" s="1"/>
+      <c r="J78" s="1"/>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
-      <c r="I79" s="1"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E79" s="1"/>
+      <c r="J79" s="1"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
-      <c r="I80" s="1"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E80" s="1"/>
+      <c r="J80" s="1"/>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
-      <c r="I81" s="1"/>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E81" s="1"/>
+      <c r="J81" s="1"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
-      <c r="I82" s="1"/>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E82" s="1"/>
+      <c r="J82" s="1"/>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
-      <c r="I83" s="1"/>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E83" s="1"/>
+      <c r="J83" s="1"/>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
-      <c r="I84" s="1"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E84" s="1"/>
+      <c r="J84" s="1"/>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
-      <c r="I85" s="1"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E85" s="1"/>
+      <c r="J85" s="1"/>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
-      <c r="I86" s="1"/>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E86" s="1"/>
+      <c r="J86" s="1"/>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
-      <c r="I87" s="1"/>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E87" s="1"/>
+      <c r="J87" s="1"/>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
-      <c r="I88" s="1"/>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E88" s="1"/>
+      <c r="J88" s="1"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
-      <c r="I89" s="1"/>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E89" s="1"/>
+      <c r="J89" s="1"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
-      <c r="I90" s="1"/>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E90" s="1"/>
+      <c r="J90" s="1"/>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
-      <c r="I91" s="1"/>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E91" s="1"/>
+      <c r="J91" s="1"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
-      <c r="I92" s="1"/>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E92" s="1"/>
+      <c r="J92" s="1"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
-      <c r="I93" s="1"/>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E93" s="1"/>
+      <c r="J93" s="1"/>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
-      <c r="I94" s="1"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E94" s="1"/>
+      <c r="J94" s="1"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
-      <c r="I95" s="1"/>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E95" s="1"/>
+      <c r="J95" s="1"/>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
-      <c r="I96" s="1"/>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E96" s="1"/>
+      <c r="J96" s="1"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
-      <c r="I97" s="1"/>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E97" s="1"/>
+      <c r="J97" s="1"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
-      <c r="I98" s="1"/>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E98" s="1"/>
+      <c r="J98" s="1"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
-      <c r="I99" s="1"/>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E99" s="1"/>
+      <c r="J99" s="1"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
-      <c r="I100" s="1"/>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E100" s="1"/>
+      <c r="J100" s="1"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
-      <c r="I101" s="1"/>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E101" s="1"/>
+      <c r="J101" s="1"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
-      <c r="I102" s="1"/>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E102" s="1"/>
+      <c r="J102" s="1"/>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
-      <c r="I103" s="1"/>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E103" s="1"/>
+      <c r="J103" s="1"/>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
-      <c r="I104" s="1"/>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E104" s="1"/>
+      <c r="J104" s="1"/>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
-      <c r="I105" s="1"/>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E105" s="1"/>
+      <c r="J105" s="1"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
-      <c r="I106" s="1"/>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E106" s="1"/>
+      <c r="J106" s="1"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
-      <c r="I107" s="1"/>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E107" s="1"/>
+      <c r="J107" s="1"/>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
-      <c r="I108" s="1"/>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E108" s="1"/>
+      <c r="J108" s="1"/>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
-      <c r="I109" s="1"/>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E109" s="1"/>
+      <c r="J109" s="1"/>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
-      <c r="I110" s="1"/>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E110" s="1"/>
+      <c r="J110" s="1"/>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
-      <c r="I111" s="1"/>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E111" s="1"/>
+      <c r="J111" s="1"/>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
-      <c r="I112" s="1"/>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E112" s="1"/>
+      <c r="J112" s="1"/>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
-      <c r="I113" s="1"/>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E113" s="1"/>
+      <c r="J113" s="1"/>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
-      <c r="I114" s="1"/>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E114" s="1"/>
+      <c r="J114" s="1"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C115" s="1"/>
       <c r="D115" s="1"/>
-      <c r="I115" s="1"/>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E115" s="1"/>
+      <c r="J115" s="1"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
-      <c r="I116" s="1"/>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E116" s="1"/>
+      <c r="J116" s="1"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
-      <c r="I117" s="1"/>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E117" s="1"/>
+      <c r="J117" s="1"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
-      <c r="I118" s="1"/>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E118" s="1"/>
+      <c r="J118" s="1"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
-      <c r="I119" s="1"/>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E119" s="1"/>
+      <c r="J119" s="1"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
-      <c r="I120" s="1"/>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E120" s="1"/>
+      <c r="J120" s="1"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
-      <c r="I121" s="1"/>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E121" s="1"/>
+      <c r="J121" s="1"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
-      <c r="I122" s="1"/>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E122" s="1"/>
+      <c r="J122" s="1"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
-      <c r="I123" s="1"/>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E123" s="1"/>
+      <c r="J123" s="1"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
-      <c r="I124" s="1"/>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E124" s="1"/>
+      <c r="J124" s="1"/>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
-      <c r="I125" s="1"/>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E125" s="1"/>
+      <c r="J125" s="1"/>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
-      <c r="I126" s="1"/>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E126" s="1"/>
+      <c r="J126" s="1"/>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
-      <c r="I127" s="1"/>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E127" s="1"/>
+      <c r="J127" s="1"/>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
-      <c r="I128" s="1"/>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E128" s="1"/>
+      <c r="J128" s="1"/>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
-      <c r="I129" s="1"/>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E129" s="1"/>
+      <c r="J129" s="1"/>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
-      <c r="I130" s="1"/>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E130" s="1"/>
+      <c r="J130" s="1"/>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
-      <c r="I131" s="1"/>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E131" s="1"/>
+      <c r="J131" s="1"/>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
-      <c r="I132" s="1"/>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E132" s="1"/>
+      <c r="J132" s="1"/>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
-      <c r="I133" s="1"/>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E133" s="1"/>
+      <c r="J133" s="1"/>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
-      <c r="I134" s="1"/>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E134" s="1"/>
+      <c r="J134" s="1"/>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C135" s="1"/>
       <c r="D135" s="1"/>
-      <c r="I135" s="1"/>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E135" s="1"/>
+      <c r="J135" s="1"/>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
-      <c r="I136" s="1"/>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E136" s="1"/>
+      <c r="J136" s="1"/>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
-      <c r="I137" s="1"/>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E137" s="1"/>
+      <c r="J137" s="1"/>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
-      <c r="I138" s="1"/>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E138" s="1"/>
+      <c r="J138" s="1"/>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
-      <c r="I139" s="1"/>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E139" s="1"/>
+      <c r="J139" s="1"/>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
-      <c r="I140" s="1"/>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E140" s="1"/>
+      <c r="J140" s="1"/>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
-      <c r="I141" s="1"/>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E141" s="1"/>
+      <c r="J141" s="1"/>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
-      <c r="I142" s="1"/>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E142" s="1"/>
+      <c r="J142" s="1"/>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
-      <c r="I143" s="1"/>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E143" s="1"/>
+      <c r="J143" s="1"/>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
-      <c r="I144" s="1"/>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E144" s="1"/>
+      <c r="J144" s="1"/>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C145" s="1"/>
       <c r="D145" s="1"/>
-      <c r="I145" s="1"/>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E145" s="1"/>
+      <c r="J145" s="1"/>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
-      <c r="I146" s="1"/>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E146" s="1"/>
+      <c r="J146" s="1"/>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
-      <c r="I147" s="1"/>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E147" s="1"/>
+      <c r="J147" s="1"/>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
-      <c r="I148" s="1"/>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E148" s="1"/>
+      <c r="J148" s="1"/>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
-      <c r="I149" s="1"/>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E149" s="1"/>
+      <c r="J149" s="1"/>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
-      <c r="I150" s="1"/>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E150" s="1"/>
+      <c r="J150" s="1"/>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C151" s="1"/>
       <c r="D151" s="1"/>
-      <c r="I151" s="1"/>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E151" s="1"/>
+      <c r="J151" s="1"/>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C152" s="1"/>
       <c r="D152" s="1"/>
-      <c r="I152" s="1"/>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E152" s="1"/>
+      <c r="J152" s="1"/>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
-      <c r="I153" s="1"/>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E153" s="1"/>
+      <c r="J153" s="1"/>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
-      <c r="I154" s="1"/>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E154" s="1"/>
+      <c r="J154" s="1"/>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
-      <c r="I155" s="1"/>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E155" s="1"/>
+      <c r="J155" s="1"/>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
-      <c r="I156" s="1"/>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E156" s="1"/>
+      <c r="J156" s="1"/>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
-      <c r="I157" s="1"/>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E157" s="1"/>
+      <c r="J157" s="1"/>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
-      <c r="I158" s="1"/>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E158" s="1"/>
+      <c r="J158" s="1"/>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C159" s="1"/>
       <c r="D159" s="1"/>
-      <c r="I159" s="1"/>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E159" s="1"/>
+      <c r="J159" s="1"/>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
-      <c r="I160" s="1"/>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E160" s="1"/>
+      <c r="J160" s="1"/>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
-      <c r="I161" s="1"/>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E161" s="1"/>
+      <c r="J161" s="1"/>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
-      <c r="I162" s="1"/>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E162" s="1"/>
+      <c r="J162" s="1"/>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C163" s="1"/>
       <c r="D163" s="1"/>
-      <c r="I163" s="1"/>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E163" s="1"/>
+      <c r="J163" s="1"/>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C164" s="1"/>
       <c r="D164" s="1"/>
-      <c r="I164" s="1"/>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E164" s="1"/>
+      <c r="J164" s="1"/>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C165" s="1"/>
       <c r="D165" s="1"/>
-      <c r="I165" s="1"/>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E165" s="1"/>
+      <c r="J165" s="1"/>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
-      <c r="I166" s="1"/>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E166" s="1"/>
+      <c r="J166" s="1"/>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
-      <c r="I167" s="1"/>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E167" s="1"/>
+      <c r="J167" s="1"/>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
-      <c r="I168" s="1"/>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E168" s="1"/>
+      <c r="J168" s="1"/>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C169" s="1"/>
       <c r="D169" s="1"/>
-      <c r="I169" s="1"/>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E169" s="1"/>
+      <c r="J169" s="1"/>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C170" s="1"/>
       <c r="D170" s="1"/>
-      <c r="I170" s="1"/>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E170" s="1"/>
+      <c r="J170" s="1"/>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C171" s="1"/>
       <c r="D171" s="1"/>
-      <c r="I171" s="1"/>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E171" s="1"/>
+      <c r="J171" s="1"/>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C172" s="1"/>
       <c r="D172" s="1"/>
-      <c r="I172" s="1"/>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E172" s="1"/>
+      <c r="J172" s="1"/>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C173" s="1"/>
       <c r="D173" s="1"/>
-      <c r="I173" s="1"/>
-    </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E173" s="1"/>
+      <c r="J173" s="1"/>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C174" s="1"/>
       <c r="D174" s="1"/>
-      <c r="I174" s="1"/>
-    </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E174" s="1"/>
+      <c r="J174" s="1"/>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C175" s="1"/>
       <c r="D175" s="1"/>
-      <c r="I175" s="1"/>
-    </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E175" s="1"/>
+      <c r="J175" s="1"/>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C176" s="1"/>
       <c r="D176" s="1"/>
-      <c r="I176" s="1"/>
-    </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E176" s="1"/>
+      <c r="J176" s="1"/>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C177" s="1"/>
       <c r="D177" s="1"/>
-      <c r="I177" s="1"/>
-    </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E177" s="1"/>
+      <c r="J177" s="1"/>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C178" s="1"/>
       <c r="D178" s="1"/>
-      <c r="I178" s="1"/>
-    </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E178" s="1"/>
+      <c r="J178" s="1"/>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C179" s="1"/>
       <c r="D179" s="1"/>
-      <c r="I179" s="1"/>
-    </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E179" s="1"/>
+      <c r="J179" s="1"/>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C180" s="1"/>
       <c r="D180" s="1"/>
-      <c r="I180" s="1"/>
-    </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E180" s="1"/>
+      <c r="J180" s="1"/>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C181" s="1"/>
       <c r="D181" s="1"/>
-      <c r="I181" s="1"/>
-    </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E181" s="1"/>
+      <c r="J181" s="1"/>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C182" s="1"/>
       <c r="D182" s="1"/>
-      <c r="I182" s="1"/>
-    </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E182" s="1"/>
+      <c r="J182" s="1"/>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C183" s="1"/>
       <c r="D183" s="1"/>
-      <c r="I183" s="1"/>
-    </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E183" s="1"/>
+      <c r="J183" s="1"/>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C184" s="1"/>
       <c r="D184" s="1"/>
-      <c r="I184" s="1"/>
-    </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E184" s="1"/>
+      <c r="J184" s="1"/>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C185" s="1"/>
       <c r="D185" s="1"/>
-      <c r="I185" s="1"/>
-    </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E185" s="1"/>
+      <c r="J185" s="1"/>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C186" s="1"/>
       <c r="D186" s="1"/>
-      <c r="I186" s="1"/>
-    </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E186" s="1"/>
+      <c r="J186" s="1"/>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C187" s="1"/>
       <c r="D187" s="1"/>
-      <c r="I187" s="1"/>
-    </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E187" s="1"/>
+      <c r="J187" s="1"/>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C188" s="1"/>
       <c r="D188" s="1"/>
-      <c r="I188" s="1"/>
-    </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E188" s="1"/>
+      <c r="J188" s="1"/>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C189" s="1"/>
       <c r="D189" s="1"/>
-      <c r="I189" s="1"/>
-    </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E189" s="1"/>
+      <c r="J189" s="1"/>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C190" s="1"/>
       <c r="D190" s="1"/>
-      <c r="I190" s="1"/>
-    </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E190" s="1"/>
+      <c r="J190" s="1"/>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C191" s="1"/>
       <c r="D191" s="1"/>
-      <c r="I191" s="1"/>
-    </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E191" s="1"/>
+      <c r="J191" s="1"/>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C192" s="1"/>
       <c r="D192" s="1"/>
-      <c r="I192" s="1"/>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E192" s="1"/>
+      <c r="J192" s="1"/>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C193" s="1"/>
       <c r="D193" s="1"/>
-      <c r="I193" s="1"/>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E193" s="1"/>
+      <c r="J193" s="1"/>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C194" s="1"/>
       <c r="D194" s="1"/>
-      <c r="I194" s="1"/>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E194" s="1"/>
+      <c r="J194" s="1"/>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C195" s="1"/>
       <c r="D195" s="1"/>
-      <c r="I195" s="1"/>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E195" s="1"/>
+      <c r="J195" s="1"/>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C196" s="1"/>
       <c r="D196" s="1"/>
-      <c r="I196" s="1"/>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E196" s="1"/>
+      <c r="J196" s="1"/>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C197" s="1"/>
       <c r="D197" s="1"/>
-      <c r="I197" s="1"/>
-    </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E197" s="1"/>
+      <c r="J197" s="1"/>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C198" s="1"/>
       <c r="D198" s="1"/>
-      <c r="I198" s="1"/>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E198" s="1"/>
+      <c r="J198" s="1"/>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C199" s="1"/>
       <c r="D199" s="1"/>
-      <c r="I199" s="1"/>
-    </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E199" s="1"/>
+      <c r="J199" s="1"/>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
-      <c r="I200" s="1"/>
-    </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E200" s="1"/>
+      <c r="J200" s="1"/>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C201" s="1"/>
       <c r="D201" s="1"/>
-      <c r="I201" s="1"/>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E201" s="1"/>
+      <c r="J201" s="1"/>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C202" s="1"/>
       <c r="D202" s="1"/>
-      <c r="I202" s="1"/>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E202" s="1"/>
+      <c r="J202" s="1"/>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C203" s="1"/>
       <c r="D203" s="1"/>
-      <c r="I203" s="1"/>
-    </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E203" s="1"/>
+      <c r="J203" s="1"/>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C204" s="1"/>
       <c r="D204" s="1"/>
-      <c r="I204" s="1"/>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E204" s="1"/>
+      <c r="J204" s="1"/>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C205" s="1"/>
       <c r="D205" s="1"/>
-      <c r="I205" s="1"/>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E205" s="1"/>
+      <c r="J205" s="1"/>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C206" s="1"/>
       <c r="D206" s="1"/>
-      <c r="I206" s="1"/>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E206" s="1"/>
+      <c r="J206" s="1"/>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C207" s="1"/>
       <c r="D207" s="1"/>
-      <c r="I207" s="1"/>
-    </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E207" s="1"/>
+      <c r="J207" s="1"/>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C208" s="1"/>
       <c r="D208" s="1"/>
-      <c r="I208" s="1"/>
-    </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E208" s="1"/>
+      <c r="J208" s="1"/>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C209" s="1"/>
       <c r="D209" s="1"/>
-      <c r="I209" s="1"/>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E209" s="1"/>
+      <c r="J209" s="1"/>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C210" s="1"/>
       <c r="D210" s="1"/>
-      <c r="I210" s="1"/>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E210" s="1"/>
+      <c r="J210" s="1"/>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C211" s="1"/>
       <c r="D211" s="1"/>
-      <c r="I211" s="1"/>
-    </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E211" s="1"/>
+      <c r="J211" s="1"/>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C212" s="1"/>
       <c r="D212" s="1"/>
-      <c r="I212" s="1"/>
-    </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E212" s="1"/>
+      <c r="J212" s="1"/>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C213" s="1"/>
       <c r="D213" s="1"/>
-      <c r="I213" s="1"/>
-    </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E213" s="1"/>
+      <c r="J213" s="1"/>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C214" s="1"/>
       <c r="D214" s="1"/>
-      <c r="I214" s="1"/>
-    </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E214" s="1"/>
+      <c r="J214" s="1"/>
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C215" s="1"/>
       <c r="D215" s="1"/>
-      <c r="I215" s="1"/>
-    </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E215" s="1"/>
+      <c r="J215" s="1"/>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C216" s="1"/>
       <c r="D216" s="1"/>
-      <c r="I216" s="1"/>
-    </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E216" s="1"/>
+      <c r="J216" s="1"/>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C217" s="1"/>
       <c r="D217" s="1"/>
-      <c r="I217" s="1"/>
-    </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E217" s="1"/>
+      <c r="J217" s="1"/>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C218" s="1"/>
       <c r="D218" s="1"/>
-      <c r="I218" s="1"/>
-    </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E218" s="1"/>
+      <c r="J218" s="1"/>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C219" s="1"/>
       <c r="D219" s="1"/>
-      <c r="I219" s="1"/>
-    </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E219" s="1"/>
+      <c r="J219" s="1"/>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C220" s="1"/>
       <c r="D220" s="1"/>
-      <c r="I220" s="1"/>
-    </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E220" s="1"/>
+      <c r="J220" s="1"/>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C221" s="1"/>
       <c r="D221" s="1"/>
-      <c r="I221" s="1"/>
-    </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E221" s="1"/>
+      <c r="J221" s="1"/>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C222" s="1"/>
       <c r="D222" s="1"/>
-      <c r="I222" s="1"/>
-    </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E222" s="1"/>
+      <c r="J222" s="1"/>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C223" s="1"/>
       <c r="D223" s="1"/>
-      <c r="I223" s="1"/>
-    </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E223" s="1"/>
+      <c r="J223" s="1"/>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C224" s="1"/>
       <c r="D224" s="1"/>
-      <c r="I224" s="1"/>
-    </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E224" s="1"/>
+      <c r="J224" s="1"/>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C225" s="1"/>
       <c r="D225" s="1"/>
-      <c r="I225" s="1"/>
-    </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E225" s="1"/>
+      <c r="J225" s="1"/>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C226" s="1"/>
       <c r="D226" s="1"/>
-      <c r="I226" s="1"/>
-    </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E226" s="1"/>
+      <c r="J226" s="1"/>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C227" s="1"/>
       <c r="D227" s="1"/>
-      <c r="I227" s="1"/>
-    </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E227" s="1"/>
+      <c r="J227" s="1"/>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C228" s="1"/>
       <c r="D228" s="1"/>
-      <c r="I228" s="1"/>
-    </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E228" s="1"/>
+      <c r="J228" s="1"/>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C229" s="1"/>
       <c r="D229" s="1"/>
-      <c r="I229" s="1"/>
-    </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E229" s="1"/>
+      <c r="J229" s="1"/>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C230" s="1"/>
       <c r="D230" s="1"/>
-      <c r="I230" s="1"/>
-    </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E230" s="1"/>
+      <c r="J230" s="1"/>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C231" s="1"/>
       <c r="D231" s="1"/>
-      <c r="I231" s="1"/>
-    </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E231" s="1"/>
+      <c r="J231" s="1"/>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C232" s="1"/>
       <c r="D232" s="1"/>
-      <c r="I232" s="1"/>
-    </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E232" s="1"/>
+      <c r="J232" s="1"/>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C233" s="1"/>
       <c r="D233" s="1"/>
-      <c r="I233" s="1"/>
-    </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E233" s="1"/>
+      <c r="J233" s="1"/>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C234" s="1"/>
       <c r="D234" s="1"/>
-      <c r="I234" s="1"/>
-    </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E234" s="1"/>
+      <c r="J234" s="1"/>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C235" s="1"/>
       <c r="D235" s="1"/>
-      <c r="I235" s="1"/>
-    </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E235" s="1"/>
+      <c r="J235" s="1"/>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C236" s="1"/>
       <c r="D236" s="1"/>
-      <c r="I236" s="1"/>
-    </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E236" s="1"/>
+      <c r="J236" s="1"/>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C237" s="1"/>
       <c r="D237" s="1"/>
-      <c r="I237" s="1"/>
-    </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E237" s="1"/>
+      <c r="J237" s="1"/>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C238" s="1"/>
       <c r="D238" s="1"/>
-      <c r="I238" s="1"/>
-    </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E238" s="1"/>
+      <c r="J238" s="1"/>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C239" s="1"/>
       <c r="D239" s="1"/>
-      <c r="I239" s="1"/>
-    </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E239" s="1"/>
+      <c r="J239" s="1"/>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C240" s="1"/>
       <c r="D240" s="1"/>
-      <c r="I240" s="1"/>
-    </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E240" s="1"/>
+      <c r="J240" s="1"/>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C241" s="1"/>
       <c r="D241" s="1"/>
-      <c r="I241" s="1"/>
-    </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E241" s="1"/>
+      <c r="J241" s="1"/>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C242" s="1"/>
       <c r="D242" s="1"/>
-      <c r="I242" s="1"/>
-    </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E242" s="1"/>
+      <c r="J242" s="1"/>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C243" s="1"/>
       <c r="D243" s="1"/>
-      <c r="I243" s="1"/>
-    </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E243" s="1"/>
+      <c r="J243" s="1"/>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C244" s="1"/>
       <c r="D244" s="1"/>
-      <c r="I244" s="1"/>
-    </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E244" s="1"/>
+      <c r="J244" s="1"/>
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C245" s="1"/>
       <c r="D245" s="1"/>
-      <c r="I245" s="1"/>
-    </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E245" s="1"/>
+      <c r="J245" s="1"/>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C246" s="1"/>
       <c r="D246" s="1"/>
-      <c r="I246" s="1"/>
-    </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E246" s="1"/>
+      <c r="J246" s="1"/>
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C247" s="1"/>
       <c r="D247" s="1"/>
-      <c r="I247" s="1"/>
-    </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E247" s="1"/>
+      <c r="J247" s="1"/>
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C248" s="1"/>
       <c r="D248" s="1"/>
-      <c r="I248" s="1"/>
-    </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E248" s="1"/>
+      <c r="J248" s="1"/>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C249" s="1"/>
       <c r="D249" s="1"/>
-      <c r="I249" s="1"/>
-    </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E249" s="1"/>
+      <c r="J249" s="1"/>
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C250" s="1"/>
       <c r="D250" s="1"/>
-      <c r="I250" s="1"/>
-    </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E250" s="1"/>
+      <c r="J250" s="1"/>
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C251" s="1"/>
       <c r="D251" s="1"/>
-      <c r="I251" s="1"/>
-    </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E251" s="1"/>
+      <c r="J251" s="1"/>
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C252" s="1"/>
       <c r="D252" s="1"/>
-      <c r="I252" s="1"/>
-    </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E252" s="1"/>
+      <c r="J252" s="1"/>
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C253" s="1"/>
       <c r="D253" s="1"/>
-      <c r="I253" s="1"/>
-    </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E253" s="1"/>
+      <c r="J253" s="1"/>
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C254" s="1"/>
       <c r="D254" s="1"/>
-      <c r="I254" s="1"/>
-    </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E254" s="1"/>
+      <c r="J254" s="1"/>
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C255" s="1"/>
       <c r="D255" s="1"/>
-      <c r="I255" s="1"/>
-    </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E255" s="1"/>
+      <c r="J255" s="1"/>
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C256" s="1"/>
       <c r="D256" s="1"/>
-      <c r="I256" s="1"/>
-    </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E256" s="1"/>
+      <c r="J256" s="1"/>
+    </row>
+    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C257" s="1"/>
       <c r="D257" s="1"/>
-      <c r="I257" s="1"/>
-    </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E257" s="1"/>
+      <c r="J257" s="1"/>
+    </row>
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C258" s="1"/>
       <c r="D258" s="1"/>
-      <c r="I258" s="1"/>
-    </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E258" s="1"/>
+      <c r="J258" s="1"/>
+    </row>
+    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C259" s="1"/>
       <c r="D259" s="1"/>
-      <c r="I259" s="1"/>
-    </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E259" s="1"/>
+      <c r="J259" s="1"/>
+    </row>
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C260" s="1"/>
       <c r="D260" s="1"/>
-      <c r="I260" s="1"/>
-    </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E260" s="1"/>
+      <c r="J260" s="1"/>
+    </row>
+    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C261" s="1"/>
       <c r="D261" s="1"/>
-      <c r="I261" s="1"/>
-    </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E261" s="1"/>
+      <c r="J261" s="1"/>
+    </row>
+    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C262" s="1"/>
       <c r="D262" s="1"/>
-      <c r="I262" s="1"/>
-    </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E262" s="1"/>
+      <c r="J262" s="1"/>
+    </row>
+    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C263" s="1"/>
       <c r="D263" s="1"/>
-      <c r="I263" s="1"/>
-    </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E263" s="1"/>
+      <c r="J263" s="1"/>
+    </row>
+    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C264" s="1"/>
       <c r="D264" s="1"/>
-      <c r="I264" s="1"/>
-    </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E264" s="1"/>
+      <c r="J264" s="1"/>
+    </row>
+    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C265" s="1"/>
       <c r="D265" s="1"/>
-      <c r="I265" s="1"/>
-    </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E265" s="1"/>
+      <c r="J265" s="1"/>
+    </row>
+    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C266" s="1"/>
       <c r="D266" s="1"/>
-      <c r="I266" s="1"/>
-    </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E266" s="1"/>
+      <c r="J266" s="1"/>
+    </row>
+    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C267" s="1"/>
       <c r="D267" s="1"/>
-      <c r="I267" s="1"/>
-    </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E267" s="1"/>
+      <c r="J267" s="1"/>
+    </row>
+    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C268" s="1"/>
       <c r="D268" s="1"/>
-      <c r="I268" s="1"/>
-    </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E268" s="1"/>
+      <c r="J268" s="1"/>
+    </row>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C269" s="1"/>
       <c r="D269" s="1"/>
-      <c r="I269" s="1"/>
-    </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E269" s="1"/>
+      <c r="J269" s="1"/>
+    </row>
+    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C270" s="1"/>
       <c r="D270" s="1"/>
-      <c r="I270" s="1"/>
-    </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E270" s="1"/>
+      <c r="J270" s="1"/>
+    </row>
+    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C271" s="1"/>
       <c r="D271" s="1"/>
-      <c r="I271" s="1"/>
-    </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E271" s="1"/>
+      <c r="J271" s="1"/>
+    </row>
+    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C272" s="1"/>
       <c r="D272" s="1"/>
-      <c r="I272" s="1"/>
-    </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E272" s="1"/>
+      <c r="J272" s="1"/>
+    </row>
+    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C273" s="1"/>
       <c r="D273" s="1"/>
-      <c r="I273" s="1"/>
-    </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E273" s="1"/>
+      <c r="J273" s="1"/>
+    </row>
+    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C274" s="1"/>
       <c r="D274" s="1"/>
-      <c r="I274" s="1"/>
-    </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E274" s="1"/>
+      <c r="J274" s="1"/>
+    </row>
+    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C275" s="1"/>
       <c r="D275" s="1"/>
-      <c r="I275" s="1"/>
-    </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E275" s="1"/>
+      <c r="J275" s="1"/>
+    </row>
+    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C276" s="1"/>
       <c r="D276" s="1"/>
-      <c r="I276" s="1"/>
-    </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E276" s="1"/>
+      <c r="J276" s="1"/>
+    </row>
+    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C277" s="1"/>
       <c r="D277" s="1"/>
-      <c r="I277" s="1"/>
-    </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E277" s="1"/>
+      <c r="J277" s="1"/>
+    </row>
+    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C278" s="1"/>
       <c r="D278" s="1"/>
-      <c r="I278" s="1"/>
-    </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E278" s="1"/>
+      <c r="J278" s="1"/>
+    </row>
+    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C279" s="1"/>
       <c r="D279" s="1"/>
-      <c r="I279" s="1"/>
-    </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E279" s="1"/>
+      <c r="J279" s="1"/>
+    </row>
+    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C280" s="1"/>
       <c r="D280" s="1"/>
-      <c r="I280" s="1"/>
-    </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E280" s="1"/>
+      <c r="J280" s="1"/>
+    </row>
+    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C281" s="1"/>
       <c r="D281" s="1"/>
-      <c r="I281" s="1"/>
-    </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E281" s="1"/>
+      <c r="J281" s="1"/>
+    </row>
+    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C282" s="1"/>
       <c r="D282" s="1"/>
-      <c r="I282" s="1"/>
-    </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E282" s="1"/>
+      <c r="J282" s="1"/>
+    </row>
+    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C283" s="1"/>
       <c r="D283" s="1"/>
-      <c r="I283" s="1"/>
-    </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E283" s="1"/>
+      <c r="J283" s="1"/>
+    </row>
+    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C284" s="1"/>
       <c r="D284" s="1"/>
-      <c r="I284" s="1"/>
-    </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E284" s="1"/>
+      <c r="J284" s="1"/>
+    </row>
+    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C285" s="1"/>
       <c r="D285" s="1"/>
-      <c r="I285" s="1"/>
-    </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E285" s="1"/>
+      <c r="J285" s="1"/>
+    </row>
+    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C286" s="1"/>
       <c r="D286" s="1"/>
-      <c r="I286" s="1"/>
-    </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E286" s="1"/>
+      <c r="J286" s="1"/>
+    </row>
+    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C287" s="1"/>
       <c r="D287" s="1"/>
-      <c r="I287" s="1"/>
-    </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E287" s="1"/>
+      <c r="J287" s="1"/>
+    </row>
+    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C288" s="1"/>
       <c r="D288" s="1"/>
-      <c r="I288" s="1"/>
-    </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E288" s="1"/>
+      <c r="J288" s="1"/>
+    </row>
+    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C289" s="1"/>
       <c r="D289" s="1"/>
-      <c r="I289" s="1"/>
-    </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E289" s="1"/>
+      <c r="J289" s="1"/>
+    </row>
+    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C290" s="1"/>
       <c r="D290" s="1"/>
-      <c r="I290" s="1"/>
-    </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E290" s="1"/>
+      <c r="J290" s="1"/>
+    </row>
+    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C291" s="1"/>
       <c r="D291" s="1"/>
-      <c r="I291" s="1"/>
-    </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E291" s="1"/>
+      <c r="J291" s="1"/>
+    </row>
+    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C292" s="1"/>
       <c r="D292" s="1"/>
-      <c r="I292" s="1"/>
-    </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E292" s="1"/>
+      <c r="J292" s="1"/>
+    </row>
+    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C293" s="1"/>
       <c r="D293" s="1"/>
-      <c r="I293" s="1"/>
-    </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E293" s="1"/>
+      <c r="J293" s="1"/>
+    </row>
+    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C294" s="1"/>
       <c r="D294" s="1"/>
-      <c r="I294" s="1"/>
-    </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E294" s="1"/>
+      <c r="J294" s="1"/>
+    </row>
+    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C295" s="1"/>
       <c r="D295" s="1"/>
-      <c r="I295" s="1"/>
-    </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E295" s="1"/>
+      <c r="J295" s="1"/>
+    </row>
+    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C296" s="1"/>
       <c r="D296" s="1"/>
-      <c r="I296" s="1"/>
-    </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E296" s="1"/>
+      <c r="J296" s="1"/>
+    </row>
+    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C297" s="1"/>
       <c r="D297" s="1"/>
-      <c r="I297" s="1"/>
-    </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E297" s="1"/>
+      <c r="J297" s="1"/>
+    </row>
+    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C298" s="1"/>
       <c r="D298" s="1"/>
-      <c r="I298" s="1"/>
-    </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E298" s="1"/>
+      <c r="J298" s="1"/>
+    </row>
+    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C299" s="1"/>
       <c r="D299" s="1"/>
-      <c r="I299" s="1"/>
-    </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E299" s="1"/>
+      <c r="J299" s="1"/>
+    </row>
+    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C300" s="1"/>
       <c r="D300" s="1"/>
-      <c r="I300" s="1"/>
-    </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E300" s="1"/>
+      <c r="J300" s="1"/>
+    </row>
+    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C301" s="1"/>
       <c r="D301" s="1"/>
-      <c r="I301" s="1"/>
-    </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E301" s="1"/>
+      <c r="J301" s="1"/>
+    </row>
+    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C302" s="1"/>
       <c r="D302" s="1"/>
-      <c r="I302" s="1"/>
-    </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E302" s="1"/>
+      <c r="J302" s="1"/>
+    </row>
+    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C303" s="1"/>
       <c r="D303" s="1"/>
-      <c r="I303" s="1"/>
-    </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E303" s="1"/>
+      <c r="J303" s="1"/>
+    </row>
+    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C304" s="1"/>
       <c r="D304" s="1"/>
-      <c r="I304" s="1"/>
-    </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E304" s="1"/>
+      <c r="J304" s="1"/>
+    </row>
+    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C305" s="1"/>
       <c r="D305" s="1"/>
-      <c r="I305" s="1"/>
-    </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E305" s="1"/>
+      <c r="J305" s="1"/>
+    </row>
+    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C306" s="1"/>
       <c r="D306" s="1"/>
-      <c r="I306" s="1"/>
-    </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E306" s="1"/>
+      <c r="J306" s="1"/>
+    </row>
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C307" s="1"/>
       <c r="D307" s="1"/>
-      <c r="I307" s="1"/>
-    </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E307" s="1"/>
+      <c r="J307" s="1"/>
+    </row>
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C308" s="1"/>
       <c r="D308" s="1"/>
-      <c r="I308" s="1"/>
-    </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E308" s="1"/>
+      <c r="J308" s="1"/>
+    </row>
+    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C309" s="1"/>
       <c r="D309" s="1"/>
-      <c r="I309" s="1"/>
-    </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E309" s="1"/>
+      <c r="J309" s="1"/>
+    </row>
+    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C310" s="1"/>
       <c r="D310" s="1"/>
-      <c r="I310" s="1"/>
-    </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E310" s="1"/>
+      <c r="J310" s="1"/>
+    </row>
+    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C311" s="1"/>
       <c r="D311" s="1"/>
-      <c r="I311" s="1"/>
-    </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E311" s="1"/>
+      <c r="J311" s="1"/>
+    </row>
+    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C312" s="1"/>
       <c r="D312" s="1"/>
-      <c r="I312" s="1"/>
-    </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E312" s="1"/>
+      <c r="J312" s="1"/>
+    </row>
+    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C313" s="1"/>
       <c r="D313" s="1"/>
-      <c r="I313" s="1"/>
-    </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E313" s="1"/>
+      <c r="J313" s="1"/>
+    </row>
+    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C314" s="1"/>
       <c r="D314" s="1"/>
-      <c r="I314" s="1"/>
-    </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E314" s="1"/>
+      <c r="J314" s="1"/>
+    </row>
+    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C315" s="1"/>
       <c r="D315" s="1"/>
-      <c r="I315" s="1"/>
-    </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E315" s="1"/>
+      <c r="J315" s="1"/>
+    </row>
+    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C316" s="1"/>
       <c r="D316" s="1"/>
-      <c r="I316" s="1"/>
-    </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E316" s="1"/>
+      <c r="J316" s="1"/>
+    </row>
+    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C317" s="1"/>
       <c r="D317" s="1"/>
-      <c r="I317" s="1"/>
-    </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E317" s="1"/>
+      <c r="J317" s="1"/>
+    </row>
+    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C318" s="1"/>
       <c r="D318" s="1"/>
-      <c r="I318" s="1"/>
-    </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E318" s="1"/>
+      <c r="J318" s="1"/>
+    </row>
+    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C319" s="1"/>
       <c r="D319" s="1"/>
-      <c r="I319" s="1"/>
-    </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E319" s="1"/>
+      <c r="J319" s="1"/>
+    </row>
+    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C320" s="1"/>
       <c r="D320" s="1"/>
-      <c r="I320" s="1"/>
-    </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E320" s="1"/>
+      <c r="J320" s="1"/>
+    </row>
+    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C321" s="1"/>
       <c r="D321" s="1"/>
-      <c r="I321" s="1"/>
-    </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E321" s="1"/>
+      <c r="J321" s="1"/>
+    </row>
+    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C322" s="1"/>
       <c r="D322" s="1"/>
-      <c r="I322" s="1"/>
-    </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E322" s="1"/>
+      <c r="J322" s="1"/>
+    </row>
+    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C323" s="1"/>
       <c r="D323" s="1"/>
-      <c r="I323" s="1"/>
-    </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E323" s="1"/>
+      <c r="J323" s="1"/>
+    </row>
+    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C324" s="1"/>
       <c r="D324" s="1"/>
-      <c r="I324" s="1"/>
-    </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E324" s="1"/>
+      <c r="J324" s="1"/>
+    </row>
+    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C325" s="1"/>
       <c r="D325" s="1"/>
-      <c r="I325" s="1"/>
-    </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E325" s="1"/>
+      <c r="J325" s="1"/>
+    </row>
+    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C326" s="1"/>
       <c r="D326" s="1"/>
-      <c r="I326" s="1"/>
-    </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E326" s="1"/>
+      <c r="J326" s="1"/>
+    </row>
+    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C327" s="1"/>
       <c r="D327" s="1"/>
-      <c r="I327" s="1"/>
-    </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E327" s="1"/>
+      <c r="J327" s="1"/>
+    </row>
+    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C328" s="1"/>
       <c r="D328" s="1"/>
-      <c r="I328" s="1"/>
-    </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E328" s="1"/>
+      <c r="J328" s="1"/>
+    </row>
+    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C329" s="1"/>
       <c r="D329" s="1"/>
-      <c r="I329" s="1"/>
-    </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E329" s="1"/>
+      <c r="J329" s="1"/>
+    </row>
+    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C330" s="1"/>
       <c r="D330" s="1"/>
-      <c r="I330" s="1"/>
-    </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E330" s="1"/>
+      <c r="J330" s="1"/>
+    </row>
+    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C331" s="1"/>
       <c r="D331" s="1"/>
-      <c r="I331" s="1"/>
-    </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E331" s="1"/>
+      <c r="J331" s="1"/>
+    </row>
+    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C332" s="1"/>
       <c r="D332" s="1"/>
-      <c r="I332" s="1"/>
-    </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E332" s="1"/>
+      <c r="J332" s="1"/>
+    </row>
+    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C333" s="1"/>
       <c r="D333" s="1"/>
-      <c r="I333" s="1"/>
-    </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E333" s="1"/>
+      <c r="J333" s="1"/>
+    </row>
+    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C334" s="1"/>
       <c r="D334" s="1"/>
-      <c r="I334" s="1"/>
-    </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E334" s="1"/>
+      <c r="J334" s="1"/>
+    </row>
+    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C335" s="1"/>
       <c r="D335" s="1"/>
-      <c r="I335" s="1"/>
-    </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E335" s="1"/>
+      <c r="J335" s="1"/>
+    </row>
+    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C336" s="1"/>
       <c r="D336" s="1"/>
-      <c r="I336" s="1"/>
-    </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E336" s="1"/>
+      <c r="J336" s="1"/>
+    </row>
+    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C337" s="1"/>
       <c r="D337" s="1"/>
-      <c r="I337" s="1"/>
-    </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E337" s="1"/>
+      <c r="J337" s="1"/>
+    </row>
+    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C338" s="1"/>
       <c r="D338" s="1"/>
-      <c r="I338" s="1"/>
-    </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E338" s="1"/>
+      <c r="J338" s="1"/>
+    </row>
+    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C339" s="1"/>
       <c r="D339" s="1"/>
-      <c r="I339" s="1"/>
-    </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E339" s="1"/>
+      <c r="J339" s="1"/>
+    </row>
+    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C340" s="1"/>
       <c r="D340" s="1"/>
-      <c r="I340" s="1"/>
-    </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E340" s="1"/>
+      <c r="J340" s="1"/>
+    </row>
+    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C341" s="1"/>
       <c r="D341" s="1"/>
-      <c r="I341" s="1"/>
-    </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E341" s="1"/>
+      <c r="J341" s="1"/>
+    </row>
+    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C342" s="1"/>
       <c r="D342" s="1"/>
-      <c r="I342" s="1"/>
-    </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E342" s="1"/>
+      <c r="J342" s="1"/>
+    </row>
+    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C343" s="1"/>
       <c r="D343" s="1"/>
-      <c r="I343" s="1"/>
-    </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E343" s="1"/>
+      <c r="J343" s="1"/>
+    </row>
+    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C344" s="1"/>
       <c r="D344" s="1"/>
-      <c r="I344" s="1"/>
-    </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E344" s="1"/>
+      <c r="J344" s="1"/>
+    </row>
+    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C345" s="1"/>
       <c r="D345" s="1"/>
-      <c r="I345" s="1"/>
-    </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E345" s="1"/>
+      <c r="J345" s="1"/>
+    </row>
+    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C346" s="1"/>
       <c r="D346" s="1"/>
-      <c r="I346" s="1"/>
-    </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E346" s="1"/>
+      <c r="J346" s="1"/>
+    </row>
+    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C347" s="1"/>
       <c r="D347" s="1"/>
-      <c r="I347" s="1"/>
-    </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E347" s="1"/>
+      <c r="J347" s="1"/>
+    </row>
+    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C348" s="1"/>
       <c r="D348" s="1"/>
-      <c r="I348" s="1"/>
-    </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E348" s="1"/>
+      <c r="J348" s="1"/>
+    </row>
+    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C349" s="1"/>
       <c r="D349" s="1"/>
-      <c r="I349" s="1"/>
-    </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E349" s="1"/>
+      <c r="J349" s="1"/>
+    </row>
+    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C350" s="1"/>
       <c r="D350" s="1"/>
-      <c r="I350" s="1"/>
-    </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E350" s="1"/>
+      <c r="J350" s="1"/>
+    </row>
+    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C351" s="1"/>
       <c r="D351" s="1"/>
-      <c r="I351" s="1"/>
-    </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E351" s="1"/>
+      <c r="J351" s="1"/>
+    </row>
+    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C352" s="1"/>
       <c r="D352" s="1"/>
-      <c r="I352" s="1"/>
-    </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E352" s="1"/>
+      <c r="J352" s="1"/>
+    </row>
+    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C353" s="1"/>
       <c r="D353" s="1"/>
-      <c r="I353" s="1"/>
-    </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E353" s="1"/>
+      <c r="J353" s="1"/>
+    </row>
+    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C354" s="1"/>
       <c r="D354" s="1"/>
-      <c r="I354" s="1"/>
-    </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E354" s="1"/>
+      <c r="J354" s="1"/>
+    </row>
+    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C355" s="1"/>
       <c r="D355" s="1"/>
-      <c r="I355" s="1"/>
-    </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E355" s="1"/>
+      <c r="J355" s="1"/>
+    </row>
+    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C356" s="1"/>
       <c r="D356" s="1"/>
-      <c r="I356" s="1"/>
-    </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E356" s="1"/>
+      <c r="J356" s="1"/>
+    </row>
+    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C357" s="1"/>
       <c r="D357" s="1"/>
-      <c r="I357" s="1"/>
-    </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E357" s="1"/>
+      <c r="J357" s="1"/>
+    </row>
+    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C358" s="1"/>
       <c r="D358" s="1"/>
-      <c r="I358" s="1"/>
-    </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E358" s="1"/>
+      <c r="J358" s="1"/>
+    </row>
+    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C359" s="1"/>
       <c r="D359" s="1"/>
-      <c r="I359" s="1"/>
-    </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E359" s="1"/>
+      <c r="J359" s="1"/>
+    </row>
+    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C360" s="1"/>
       <c r="D360" s="1"/>
-      <c r="I360" s="1"/>
-    </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E360" s="1"/>
+      <c r="J360" s="1"/>
+    </row>
+    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C361" s="1"/>
       <c r="D361" s="1"/>
-      <c r="I361" s="1"/>
-    </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E361" s="1"/>
+      <c r="J361" s="1"/>
+    </row>
+    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C362" s="1"/>
       <c r="D362" s="1"/>
-      <c r="I362" s="1"/>
-    </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E362" s="1"/>
+      <c r="J362" s="1"/>
+    </row>
+    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C363" s="1"/>
       <c r="D363" s="1"/>
-      <c r="I363" s="1"/>
-    </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E363" s="1"/>
+      <c r="J363" s="1"/>
+    </row>
+    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C364" s="1"/>
       <c r="D364" s="1"/>
-      <c r="I364" s="1"/>
-    </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E364" s="1"/>
+      <c r="J364" s="1"/>
+    </row>
+    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C365" s="1"/>
       <c r="D365" s="1"/>
-      <c r="I365" s="1"/>
-    </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E365" s="1"/>
+      <c r="J365" s="1"/>
+    </row>
+    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C366" s="1"/>
       <c r="D366" s="1"/>
-      <c r="I366" s="1"/>
-    </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E366" s="1"/>
+      <c r="J366" s="1"/>
+    </row>
+    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C367" s="1"/>
       <c r="D367" s="1"/>
-      <c r="I367" s="1"/>
-    </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E367" s="1"/>
+      <c r="J367" s="1"/>
+    </row>
+    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C368" s="1"/>
       <c r="D368" s="1"/>
-      <c r="I368" s="1"/>
-    </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E368" s="1"/>
+      <c r="J368" s="1"/>
+    </row>
+    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C369" s="1"/>
       <c r="D369" s="1"/>
-      <c r="I369" s="1"/>
-    </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E369" s="1"/>
+      <c r="J369" s="1"/>
+    </row>
+    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C370" s="1"/>
       <c r="D370" s="1"/>
-      <c r="I370" s="1"/>
-    </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E370" s="1"/>
+      <c r="J370" s="1"/>
+    </row>
+    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C371" s="1"/>
       <c r="D371" s="1"/>
-      <c r="I371" s="1"/>
-    </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E371" s="1"/>
+      <c r="J371" s="1"/>
+    </row>
+    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C372" s="1"/>
       <c r="D372" s="1"/>
-      <c r="I372" s="1"/>
-    </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E372" s="1"/>
+      <c r="J372" s="1"/>
+    </row>
+    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C373" s="1"/>
       <c r="D373" s="1"/>
-      <c r="I373" s="1"/>
-    </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E373" s="1"/>
+      <c r="J373" s="1"/>
+    </row>
+    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C374" s="1"/>
       <c r="D374" s="1"/>
-      <c r="I374" s="1"/>
-    </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E374" s="1"/>
+      <c r="J374" s="1"/>
+    </row>
+    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C375" s="1"/>
       <c r="D375" s="1"/>
-      <c r="I375" s="1"/>
-    </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E375" s="1"/>
+      <c r="J375" s="1"/>
+    </row>
+    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C376" s="1"/>
       <c r="D376" s="1"/>
-      <c r="I376" s="1"/>
-    </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E376" s="1"/>
+      <c r="J376" s="1"/>
+    </row>
+    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C377" s="1"/>
       <c r="D377" s="1"/>
-      <c r="I377" s="1"/>
-    </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E377" s="1"/>
+      <c r="J377" s="1"/>
+    </row>
+    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C378" s="1"/>
       <c r="D378" s="1"/>
-      <c r="I378" s="1"/>
-    </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E378" s="1"/>
+      <c r="J378" s="1"/>
+    </row>
+    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C379" s="1"/>
       <c r="D379" s="1"/>
-      <c r="I379" s="1"/>
-    </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E379" s="1"/>
+      <c r="J379" s="1"/>
+    </row>
+    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C380" s="1"/>
       <c r="D380" s="1"/>
-      <c r="I380" s="1"/>
-    </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E380" s="1"/>
+      <c r="J380" s="1"/>
+    </row>
+    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C381" s="1"/>
       <c r="D381" s="1"/>
-      <c r="I381" s="1"/>
-    </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E381" s="1"/>
+      <c r="J381" s="1"/>
+    </row>
+    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C382" s="1"/>
       <c r="D382" s="1"/>
-      <c r="I382" s="1"/>
-    </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E382" s="1"/>
+      <c r="J382" s="1"/>
+    </row>
+    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C383" s="1"/>
       <c r="D383" s="1"/>
-      <c r="I383" s="1"/>
-    </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E383" s="1"/>
+      <c r="J383" s="1"/>
+    </row>
+    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C384" s="1"/>
       <c r="D384" s="1"/>
-      <c r="I384" s="1"/>
-    </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E384" s="1"/>
+      <c r="J384" s="1"/>
+    </row>
+    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C385" s="1"/>
       <c r="D385" s="1"/>
-      <c r="I385" s="1"/>
-    </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E385" s="1"/>
+      <c r="J385" s="1"/>
+    </row>
+    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C386" s="1"/>
       <c r="D386" s="1"/>
-      <c r="I386" s="1"/>
-    </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E386" s="1"/>
+      <c r="J386" s="1"/>
+    </row>
+    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C387" s="1"/>
       <c r="D387" s="1"/>
-      <c r="I387" s="1"/>
-    </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E387" s="1"/>
+      <c r="J387" s="1"/>
+    </row>
+    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C388" s="1"/>
       <c r="D388" s="1"/>
-      <c r="I388" s="1"/>
-    </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E388" s="1"/>
+      <c r="J388" s="1"/>
+    </row>
+    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C389" s="1"/>
       <c r="D389" s="1"/>
-      <c r="I389" s="1"/>
-    </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E389" s="1"/>
+      <c r="J389" s="1"/>
+    </row>
+    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C390" s="1"/>
       <c r="D390" s="1"/>
-      <c r="I390" s="1"/>
-    </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E390" s="1"/>
+      <c r="J390" s="1"/>
+    </row>
+    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C391" s="1"/>
       <c r="D391" s="1"/>
-      <c r="I391" s="1"/>
-    </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E391" s="1"/>
+      <c r="J391" s="1"/>
+    </row>
+    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C392" s="1"/>
       <c r="D392" s="1"/>
-      <c r="I392" s="1"/>
-    </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E392" s="1"/>
+      <c r="J392" s="1"/>
+    </row>
+    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C393" s="1"/>
       <c r="D393" s="1"/>
-      <c r="I393" s="1"/>
-    </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E393" s="1"/>
+      <c r="J393" s="1"/>
+    </row>
+    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C394" s="1"/>
       <c r="D394" s="1"/>
-      <c r="I394" s="1"/>
-    </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E394" s="1"/>
+      <c r="J394" s="1"/>
+    </row>
+    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C395" s="1"/>
       <c r="D395" s="1"/>
-      <c r="I395" s="1"/>
-    </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E395" s="1"/>
+      <c r="J395" s="1"/>
+    </row>
+    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C396" s="1"/>
       <c r="D396" s="1"/>
-      <c r="I396" s="1"/>
-    </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E396" s="1"/>
+      <c r="J396" s="1"/>
+    </row>
+    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C397" s="1"/>
       <c r="D397" s="1"/>
-      <c r="I397" s="1"/>
-    </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E397" s="1"/>
+      <c r="J397" s="1"/>
+    </row>
+    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C398" s="1"/>
       <c r="D398" s="1"/>
-      <c r="I398" s="1"/>
-    </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E398" s="1"/>
+      <c r="J398" s="1"/>
+    </row>
+    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C399" s="1"/>
       <c r="D399" s="1"/>
-      <c r="I399" s="1"/>
-    </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E399" s="1"/>
+      <c r="J399" s="1"/>
+    </row>
+    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C400" s="1"/>
       <c r="D400" s="1"/>
-      <c r="I400" s="1"/>
-    </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E400" s="1"/>
+      <c r="J400" s="1"/>
+    </row>
+    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C401" s="1"/>
       <c r="D401" s="1"/>
-      <c r="I401" s="1"/>
-    </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E401" s="1"/>
+      <c r="J401" s="1"/>
+    </row>
+    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C402" s="1"/>
       <c r="D402" s="1"/>
-      <c r="I402" s="1"/>
-    </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E402" s="1"/>
+      <c r="J402" s="1"/>
+    </row>
+    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C403" s="1"/>
       <c r="D403" s="1"/>
-      <c r="I403" s="1"/>
-    </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E403" s="1"/>
+      <c r="J403" s="1"/>
+    </row>
+    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C404" s="1"/>
       <c r="D404" s="1"/>
-      <c r="I404" s="1"/>
-    </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E404" s="1"/>
+      <c r="J404" s="1"/>
+    </row>
+    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C405" s="1"/>
       <c r="D405" s="1"/>
-      <c r="I405" s="1"/>
-    </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E405" s="1"/>
+      <c r="J405" s="1"/>
+    </row>
+    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C406" s="1"/>
       <c r="D406" s="1"/>
-      <c r="I406" s="1"/>
-    </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E406" s="1"/>
+      <c r="J406" s="1"/>
+    </row>
+    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C407" s="1"/>
       <c r="D407" s="1"/>
-      <c r="I407" s="1"/>
-    </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E407" s="1"/>
+      <c r="J407" s="1"/>
+    </row>
+    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C408" s="1"/>
       <c r="D408" s="1"/>
-      <c r="I408" s="1"/>
-    </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E408" s="1"/>
+      <c r="J408" s="1"/>
+    </row>
+    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C409" s="1"/>
       <c r="D409" s="1"/>
-      <c r="I409" s="1"/>
-    </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E409" s="1"/>
+      <c r="J409" s="1"/>
+    </row>
+    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C410" s="1"/>
       <c r="D410" s="1"/>
-      <c r="I410" s="1"/>
-    </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E410" s="1"/>
+      <c r="J410" s="1"/>
+    </row>
+    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C411" s="1"/>
       <c r="D411" s="1"/>
-      <c r="I411" s="1"/>
-    </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E411" s="1"/>
+      <c r="J411" s="1"/>
+    </row>
+    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C412" s="1"/>
       <c r="D412" s="1"/>
-      <c r="I412" s="1"/>
-    </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E412" s="1"/>
+      <c r="J412" s="1"/>
+    </row>
+    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C413" s="1"/>
       <c r="D413" s="1"/>
-      <c r="I413" s="1"/>
-    </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E413" s="1"/>
+      <c r="J413" s="1"/>
+    </row>
+    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C414" s="1"/>
       <c r="D414" s="1"/>
-      <c r="I414" s="1"/>
-    </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E414" s="1"/>
+      <c r="J414" s="1"/>
+    </row>
+    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C415" s="1"/>
       <c r="D415" s="1"/>
-      <c r="I415" s="1"/>
-    </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E415" s="1"/>
+      <c r="J415" s="1"/>
+    </row>
+    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C416" s="1"/>
       <c r="D416" s="1"/>
-      <c r="I416" s="1"/>
-    </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E416" s="1"/>
+      <c r="J416" s="1"/>
+    </row>
+    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C417" s="1"/>
       <c r="D417" s="1"/>
-      <c r="I417" s="1"/>
-    </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E417" s="1"/>
+      <c r="J417" s="1"/>
+    </row>
+    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C418" s="1"/>
       <c r="D418" s="1"/>
-      <c r="I418" s="1"/>
-    </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E418" s="1"/>
+      <c r="J418" s="1"/>
+    </row>
+    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C419" s="1"/>
       <c r="D419" s="1"/>
-      <c r="I419" s="1"/>
-    </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E419" s="1"/>
+      <c r="J419" s="1"/>
+    </row>
+    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C420" s="1"/>
       <c r="D420" s="1"/>
-      <c r="I420" s="1"/>
-    </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E420" s="1"/>
+      <c r="J420" s="1"/>
+    </row>
+    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C421" s="1"/>
       <c r="D421" s="1"/>
-      <c r="I421" s="1"/>
-    </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E421" s="1"/>
+      <c r="J421" s="1"/>
+    </row>
+    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C422" s="1"/>
       <c r="D422" s="1"/>
-      <c r="I422" s="1"/>
-    </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E422" s="1"/>
+      <c r="J422" s="1"/>
+    </row>
+    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C423" s="1"/>
       <c r="D423" s="1"/>
-      <c r="I423" s="1"/>
-    </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E423" s="1"/>
+      <c r="J423" s="1"/>
+    </row>
+    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C424" s="1"/>
       <c r="D424" s="1"/>
-      <c r="I424" s="1"/>
-    </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E424" s="1"/>
+      <c r="J424" s="1"/>
+    </row>
+    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C425" s="1"/>
       <c r="D425" s="1"/>
-      <c r="I425" s="1"/>
-    </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E425" s="1"/>
+      <c r="J425" s="1"/>
+    </row>
+    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C426" s="1"/>
       <c r="D426" s="1"/>
-      <c r="I426" s="1"/>
-    </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E426" s="1"/>
+      <c r="J426" s="1"/>
+    </row>
+    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C427" s="1"/>
       <c r="D427" s="1"/>
-      <c r="I427" s="1"/>
-    </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E427" s="1"/>
+      <c r="J427" s="1"/>
+    </row>
+    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C428" s="1"/>
       <c r="D428" s="1"/>
-      <c r="I428" s="1"/>
-    </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E428" s="1"/>
+      <c r="J428" s="1"/>
+    </row>
+    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C429" s="1"/>
       <c r="D429" s="1"/>
-      <c r="I429" s="1"/>
-    </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E429" s="1"/>
+      <c r="J429" s="1"/>
+    </row>
+    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C430" s="1"/>
       <c r="D430" s="1"/>
-      <c r="I430" s="1"/>
-    </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E430" s="1"/>
+      <c r="J430" s="1"/>
+    </row>
+    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C431" s="1"/>
       <c r="D431" s="1"/>
-      <c r="I431" s="1"/>
-    </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E431" s="1"/>
+      <c r="J431" s="1"/>
+    </row>
+    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C432" s="1"/>
       <c r="D432" s="1"/>
-      <c r="I432" s="1"/>
-    </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E432" s="1"/>
+      <c r="J432" s="1"/>
+    </row>
+    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C433" s="1"/>
       <c r="D433" s="1"/>
-      <c r="I433" s="1"/>
-    </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E433" s="1"/>
+      <c r="J433" s="1"/>
+    </row>
+    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C434" s="1"/>
       <c r="D434" s="1"/>
-      <c r="I434" s="1"/>
-    </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E434" s="1"/>
+      <c r="J434" s="1"/>
+    </row>
+    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C435" s="1"/>
       <c r="D435" s="1"/>
-      <c r="I435" s="1"/>
-    </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E435" s="1"/>
+      <c r="J435" s="1"/>
+    </row>
+    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C436" s="1"/>
       <c r="D436" s="1"/>
-      <c r="I436" s="1"/>
-    </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E436" s="1"/>
+      <c r="J436" s="1"/>
+    </row>
+    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C437" s="1"/>
       <c r="D437" s="1"/>
-      <c r="I437" s="1"/>
-    </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E437" s="1"/>
+      <c r="J437" s="1"/>
+    </row>
+    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C438" s="1"/>
       <c r="D438" s="1"/>
-      <c r="I438" s="1"/>
-    </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E438" s="1"/>
+      <c r="J438" s="1"/>
+    </row>
+    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C439" s="1"/>
       <c r="D439" s="1"/>
-      <c r="I439" s="1"/>
-    </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E439" s="1"/>
+      <c r="J439" s="1"/>
+    </row>
+    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C440" s="1"/>
       <c r="D440" s="1"/>
-      <c r="I440" s="1"/>
-    </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E440" s="1"/>
+      <c r="J440" s="1"/>
+    </row>
+    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C441" s="1"/>
       <c r="D441" s="1"/>
-      <c r="I441" s="1"/>
-    </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E441" s="1"/>
+      <c r="J441" s="1"/>
+    </row>
+    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C442" s="1"/>
       <c r="D442" s="1"/>
-      <c r="I442" s="1"/>
-    </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E442" s="1"/>
+      <c r="J442" s="1"/>
+    </row>
+    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C443" s="1"/>
       <c r="D443" s="1"/>
-      <c r="I443" s="1"/>
-    </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E443" s="1"/>
+      <c r="J443" s="1"/>
+    </row>
+    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C444" s="1"/>
       <c r="D444" s="1"/>
-      <c r="I444" s="1"/>
-    </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E444" s="1"/>
+      <c r="J444" s="1"/>
+    </row>
+    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C445" s="1"/>
       <c r="D445" s="1"/>
-      <c r="I445" s="1"/>
-    </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E445" s="1"/>
+      <c r="J445" s="1"/>
+    </row>
+    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C446" s="1"/>
       <c r="D446" s="1"/>
-      <c r="I446" s="1"/>
-    </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E446" s="1"/>
+      <c r="J446" s="1"/>
+    </row>
+    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C447" s="1"/>
       <c r="D447" s="1"/>
-      <c r="I447" s="1"/>
-    </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E447" s="1"/>
+      <c r="J447" s="1"/>
+    </row>
+    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C448" s="1"/>
       <c r="D448" s="1"/>
-      <c r="I448" s="1"/>
-    </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E448" s="1"/>
+      <c r="J448" s="1"/>
+    </row>
+    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C449" s="1"/>
       <c r="D449" s="1"/>
-      <c r="I449" s="1"/>
-    </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E449" s="1"/>
+      <c r="J449" s="1"/>
+    </row>
+    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C450" s="1"/>
       <c r="D450" s="1"/>
-      <c r="I450" s="1"/>
-    </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E450" s="1"/>
+      <c r="J450" s="1"/>
+    </row>
+    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C451" s="1"/>
       <c r="D451" s="1"/>
-      <c r="I451" s="1"/>
-    </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E451" s="1"/>
+      <c r="J451" s="1"/>
+    </row>
+    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C452" s="1"/>
       <c r="D452" s="1"/>
-      <c r="I452" s="1"/>
-    </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E452" s="1"/>
+      <c r="J452" s="1"/>
+    </row>
+    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C453" s="1"/>
       <c r="D453" s="1"/>
-      <c r="I453" s="1"/>
-    </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E453" s="1"/>
+      <c r="J453" s="1"/>
+    </row>
+    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C454" s="1"/>
       <c r="D454" s="1"/>
-      <c r="I454" s="1"/>
-    </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E454" s="1"/>
+      <c r="J454" s="1"/>
+    </row>
+    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C455" s="1"/>
       <c r="D455" s="1"/>
-      <c r="I455" s="1"/>
-    </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E455" s="1"/>
+      <c r="J455" s="1"/>
+    </row>
+    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C456" s="1"/>
       <c r="D456" s="1"/>
-      <c r="I456" s="1"/>
-    </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E456" s="1"/>
+      <c r="J456" s="1"/>
+    </row>
+    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C457" s="1"/>
       <c r="D457" s="1"/>
-      <c r="I457" s="1"/>
-    </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E457" s="1"/>
+      <c r="J457" s="1"/>
+    </row>
+    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C458" s="1"/>
       <c r="D458" s="1"/>
-      <c r="I458" s="1"/>
-    </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E458" s="1"/>
+      <c r="J458" s="1"/>
+    </row>
+    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C459" s="1"/>
       <c r="D459" s="1"/>
-      <c r="I459" s="1"/>
-    </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E459" s="1"/>
+      <c r="J459" s="1"/>
+    </row>
+    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C460" s="1"/>
       <c r="D460" s="1"/>
-      <c r="I460" s="1"/>
-    </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E460" s="1"/>
+      <c r="J460" s="1"/>
+    </row>
+    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C461" s="1"/>
       <c r="D461" s="1"/>
-      <c r="I461" s="1"/>
-    </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E461" s="1"/>
+      <c r="J461" s="1"/>
+    </row>
+    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C462" s="1"/>
       <c r="D462" s="1"/>
-      <c r="I462" s="1"/>
-    </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E462" s="1"/>
+      <c r="J462" s="1"/>
+    </row>
+    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C463" s="1"/>
       <c r="D463" s="1"/>
-      <c r="I463" s="1"/>
-    </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E463" s="1"/>
+      <c r="J463" s="1"/>
+    </row>
+    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C464" s="1"/>
       <c r="D464" s="1"/>
-      <c r="I464" s="1"/>
-    </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E464" s="1"/>
+      <c r="J464" s="1"/>
+    </row>
+    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C465" s="1"/>
       <c r="D465" s="1"/>
-      <c r="I465" s="1"/>
-    </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E465" s="1"/>
+      <c r="J465" s="1"/>
+    </row>
+    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C466" s="1"/>
       <c r="D466" s="1"/>
-      <c r="I466" s="1"/>
-    </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E466" s="1"/>
+      <c r="J466" s="1"/>
+    </row>
+    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C467" s="1"/>
       <c r="D467" s="1"/>
-      <c r="I467" s="1"/>
-    </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E467" s="1"/>
+      <c r="J467" s="1"/>
+    </row>
+    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C468" s="1"/>
       <c r="D468" s="1"/>
-      <c r="I468" s="1"/>
-    </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E468" s="1"/>
+      <c r="J468" s="1"/>
+    </row>
+    <row r="469" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C469" s="1"/>
       <c r="D469" s="1"/>
-      <c r="I469" s="1"/>
-    </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E469" s="1"/>
+      <c r="J469" s="1"/>
+    </row>
+    <row r="470" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C470" s="1"/>
       <c r="D470" s="1"/>
-      <c r="I470" s="1"/>
-    </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E470" s="1"/>
+      <c r="J470" s="1"/>
+    </row>
+    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C471" s="1"/>
       <c r="D471" s="1"/>
-      <c r="I471" s="1"/>
-    </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E471" s="1"/>
+      <c r="J471" s="1"/>
+    </row>
+    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C472" s="1"/>
       <c r="D472" s="1"/>
-      <c r="I472" s="1"/>
-    </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E472" s="1"/>
+      <c r="J472" s="1"/>
+    </row>
+    <row r="473" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C473" s="1"/>
       <c r="D473" s="1"/>
-      <c r="I473" s="1"/>
-    </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E473" s="1"/>
+      <c r="J473" s="1"/>
+    </row>
+    <row r="474" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C474" s="1"/>
       <c r="D474" s="1"/>
-      <c r="I474" s="1"/>
-    </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E474" s="1"/>
+      <c r="J474" s="1"/>
+    </row>
+    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C475" s="1"/>
       <c r="D475" s="1"/>
-      <c r="I475" s="1"/>
-    </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E475" s="1"/>
+      <c r="J475" s="1"/>
+    </row>
+    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C476" s="1"/>
       <c r="D476" s="1"/>
-      <c r="I476" s="1"/>
-    </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E476" s="1"/>
+      <c r="J476" s="1"/>
+    </row>
+    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C477" s="1"/>
       <c r="D477" s="1"/>
-      <c r="I477" s="1"/>
-    </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E477" s="1"/>
+      <c r="J477" s="1"/>
+    </row>
+    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C478" s="1"/>
       <c r="D478" s="1"/>
-      <c r="I478" s="1"/>
-    </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E478" s="1"/>
+      <c r="J478" s="1"/>
+    </row>
+    <row r="479" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C479" s="1"/>
       <c r="D479" s="1"/>
-      <c r="I479" s="1"/>
-    </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E479" s="1"/>
+      <c r="J479" s="1"/>
+    </row>
+    <row r="480" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C480" s="1"/>
       <c r="D480" s="1"/>
-      <c r="I480" s="1"/>
-    </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E480" s="1"/>
+      <c r="J480" s="1"/>
+    </row>
+    <row r="481" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C481" s="1"/>
       <c r="D481" s="1"/>
-      <c r="I481" s="1"/>
-    </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E481" s="1"/>
+      <c r="J481" s="1"/>
+    </row>
+    <row r="482" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C482" s="1"/>
       <c r="D482" s="1"/>
-      <c r="I482" s="1"/>
-    </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E482" s="1"/>
+      <c r="J482" s="1"/>
+    </row>
+    <row r="483" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C483" s="1"/>
       <c r="D483" s="1"/>
-      <c r="I483" s="1"/>
-    </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E483" s="1"/>
+      <c r="J483" s="1"/>
+    </row>
+    <row r="484" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C484" s="1"/>
       <c r="D484" s="1"/>
-      <c r="I484" s="1"/>
-    </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E484" s="1"/>
+      <c r="J484" s="1"/>
+    </row>
+    <row r="485" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C485" s="1"/>
       <c r="D485" s="1"/>
-      <c r="I485" s="1"/>
-    </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E485" s="1"/>
+      <c r="J485" s="1"/>
+    </row>
+    <row r="486" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C486" s="1"/>
       <c r="D486" s="1"/>
-      <c r="I486" s="1"/>
-    </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E486" s="1"/>
+      <c r="J486" s="1"/>
+    </row>
+    <row r="487" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C487" s="1"/>
       <c r="D487" s="1"/>
-      <c r="I487" s="1"/>
-    </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E487" s="1"/>
+      <c r="J487" s="1"/>
+    </row>
+    <row r="488" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C488" s="1"/>
       <c r="D488" s="1"/>
-      <c r="I488" s="1"/>
-    </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E488" s="1"/>
+      <c r="J488" s="1"/>
+    </row>
+    <row r="489" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C489" s="1"/>
       <c r="D489" s="1"/>
-      <c r="I489" s="1"/>
-    </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E489" s="1"/>
+      <c r="J489" s="1"/>
+    </row>
+    <row r="490" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C490" s="1"/>
       <c r="D490" s="1"/>
-      <c r="I490" s="1"/>
-    </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E490" s="1"/>
+      <c r="J490" s="1"/>
+    </row>
+    <row r="491" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C491" s="1"/>
       <c r="D491" s="1"/>
-      <c r="I491" s="1"/>
-    </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E491" s="1"/>
+      <c r="J491" s="1"/>
+    </row>
+    <row r="492" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C492" s="1"/>
       <c r="D492" s="1"/>
-      <c r="I492" s="1"/>
-    </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E492" s="1"/>
+      <c r="J492" s="1"/>
+    </row>
+    <row r="493" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C493" s="1"/>
       <c r="D493" s="1"/>
-      <c r="I493" s="1"/>
-    </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E493" s="1"/>
+      <c r="J493" s="1"/>
+    </row>
+    <row r="494" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C494" s="1"/>
       <c r="D494" s="1"/>
-      <c r="I494" s="1"/>
-    </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E494" s="1"/>
+      <c r="J494" s="1"/>
+    </row>
+    <row r="495" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C495" s="1"/>
       <c r="D495" s="1"/>
-      <c r="I495" s="1"/>
-    </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E495" s="1"/>
+      <c r="J495" s="1"/>
+    </row>
+    <row r="496" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C496" s="1"/>
       <c r="D496" s="1"/>
-      <c r="I496" s="1"/>
-    </row>
-    <row r="497" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E496" s="1"/>
+      <c r="J496" s="1"/>
+    </row>
+    <row r="497" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C497" s="1"/>
       <c r="D497" s="1"/>
-      <c r="I497" s="1"/>
-    </row>
-    <row r="498" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E497" s="1"/>
+      <c r="J497" s="1"/>
+    </row>
+    <row r="498" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C498" s="1"/>
       <c r="D498" s="1"/>
-      <c r="I498" s="1"/>
-    </row>
-    <row r="499" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E498" s="1"/>
+      <c r="J498" s="1"/>
+    </row>
+    <row r="499" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C499" s="1"/>
       <c r="D499" s="1"/>
-      <c r="I499" s="1"/>
-    </row>
-    <row r="500" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E499" s="1"/>
+      <c r="J499" s="1"/>
+    </row>
+    <row r="500" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C500" s="1"/>
       <c r="D500" s="1"/>
-      <c r="I500" s="1"/>
-    </row>
-    <row r="501" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E500" s="1"/>
+      <c r="J500" s="1"/>
+    </row>
+    <row r="501" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C501" s="1"/>
       <c r="D501" s="1"/>
-      <c r="I501" s="1"/>
+      <c r="E501" s="1"/>
+      <c r="J501" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Gender" error="Choose Male or Female." sqref="E10:E501">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Gender" error="Choose Male or Female." sqref="F10:F501">
       <formula1>"Male,Female"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Gender" error="Choose Male or Female." sqref="E2:E501">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Gender" error="Choose Male or Female." sqref="F2:F501">
       <formula1>"Male,Female"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3202,194 +3716,194 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
